--- a/data/trans_orig/P1423-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1423-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2007</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18151</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23189</t>
+          <t>24550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46694</t>
+          <t>47234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259207</t>
+          <t>260028</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269405</t>
+          <t>270105</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>222656</t>
+          <t>222364</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242687</t>
+          <t>243849</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>487154</t>
+          <t>486614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>510659</t>
+          <t>509298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20363</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34186</t>
+          <t>32984</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59764</t>
+          <t>59584</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44434</t>
+          <t>45587</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73787</t>
+          <t>74064</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472712</t>
+          <t>472479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>486232</t>
+          <t>487033</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>444185</t>
+          <t>444365</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>469763</t>
+          <t>470965</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>923237</t>
+          <t>922960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952590</t>
+          <t>951437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>14309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33443</t>
+          <t>32751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16986</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37848</t>
+          <t>37947</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308384</t>
+          <t>307306</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317904</t>
+          <t>317900</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>301969</t>
+          <t>302661</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321036</t>
+          <t>321103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616410</t>
+          <t>616311</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>637272</t>
+          <t>637045</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10019</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26499</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16096</t>
+          <t>15720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36098</t>
+          <t>35181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343598</t>
+          <t>343051</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355936</t>
+          <t>355335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>344957</t>
+          <t>345011</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361437</t>
+          <t>361151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>694029</t>
+          <t>694946</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>714031</t>
+          <t>714407</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14128</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13257</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31455</t>
+          <t>32237</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>19139</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39082</t>
+          <t>40265</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189180</t>
+          <t>190819</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199937</t>
+          <t>199899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176213</t>
+          <t>175431</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194411</t>
+          <t>193261</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>371894</t>
+          <t>370711</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392384</t>
+          <t>391837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25068</t>
+          <t>23792</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27593</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264279</t>
+          <t>264578</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253076</t>
+          <t>254352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269694</t>
+          <t>269016</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>521362</t>
+          <t>521580</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>538698</t>
+          <t>538567</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27615</t>
+          <t>27065</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39724</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68592</t>
+          <t>66033</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54734</t>
+          <t>54500</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87443</t>
+          <t>86196</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>587412</t>
+          <t>587962</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>603607</t>
+          <t>603618</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>569627</t>
+          <t>572186</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>598495</t>
+          <t>599886</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1165803</t>
+          <t>1167050</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1198512</t>
+          <t>1198746</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31747</t>
+          <t>32070</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56377</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44323</t>
+          <t>44506</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75351</t>
+          <t>73742</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82102</t>
+          <t>82536</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>121521</t>
+          <t>124677</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>687418</t>
+          <t>684748</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>712048</t>
+          <t>711725</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>708160</t>
+          <t>709769</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>739188</t>
+          <t>739005</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1405785</t>
+          <t>1402629</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1445204</t>
+          <t>1444770</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>82495</t>
+          <t>82672</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>121211</t>
+          <t>122507</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>226831</t>
+          <t>226997</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>288464</t>
+          <t>288276</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>324573</t>
+          <t>326547</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>398476</t>
+          <t>396959</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3155332</t>
+          <t>3154036</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3194048</t>
+          <t>3193871</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3090733</t>
+          <t>3090921</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3152366</t>
+          <t>3152200</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6257265</t>
+          <t>6258782</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6331168</t>
+          <t>6329194</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2012</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25380</t>
+          <t>25101</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48982</t>
+          <t>47980</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38600</t>
+          <t>37889</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65547</t>
+          <t>65386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271011</t>
+          <t>271327</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286218</t>
+          <t>286248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>238263</t>
+          <t>239265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261865</t>
+          <t>262144</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516436</t>
+          <t>516597</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>543383</t>
+          <t>544094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10590</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31647</t>
+          <t>33408</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50273</t>
+          <t>50001</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81783</t>
+          <t>82553</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66666</t>
+          <t>66445</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103694</t>
+          <t>104817</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>473880</t>
+          <t>472119</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494937</t>
+          <t>494674</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441982</t>
+          <t>441212</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>473492</t>
+          <t>473764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>925598</t>
+          <t>924475</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>962626</t>
+          <t>962847</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27200</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27951</t>
+          <t>27581</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51256</t>
+          <t>52107</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42082</t>
+          <t>41665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71269</t>
+          <t>69788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296846</t>
+          <t>296139</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314352</t>
+          <t>314011</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>289764</t>
+          <t>288913</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>313069</t>
+          <t>313439</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>593797</t>
+          <t>595278</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>622984</t>
+          <t>623401</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20326</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40651</t>
+          <t>41560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66570</t>
+          <t>68534</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48999</t>
+          <t>46929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79166</t>
+          <t>79202</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353656</t>
+          <t>356754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369748</t>
+          <t>369842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>322381</t>
+          <t>320417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348300</t>
+          <t>347391</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>683767</t>
+          <t>683731</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>713934</t>
+          <t>716004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34547</t>
+          <t>33536</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58982</t>
+          <t>57497</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41927</t>
+          <t>41275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70073</t>
+          <t>70252</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194248</t>
+          <t>193628</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207435</t>
+          <t>207502</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160609</t>
+          <t>162094</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185044</t>
+          <t>186055</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>362136</t>
+          <t>361957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>390282</t>
+          <t>390934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,45%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>24099</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26540</t>
+          <t>27395</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49330</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38294</t>
+          <t>37615</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67632</t>
+          <t>66153</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249007</t>
+          <t>249882</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265935</t>
+          <t>266022</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>228766</t>
+          <t>228405</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251556</t>
+          <t>250701</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>484445</t>
+          <t>485924</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>513783</t>
+          <t>514462</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23940</t>
+          <t>23622</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47666</t>
+          <t>49699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48652</t>
+          <t>48795</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78810</t>
+          <t>78056</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80430</t>
+          <t>78896</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117838</t>
+          <t>120523</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>615122</t>
+          <t>613089</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638848</t>
+          <t>639166</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>615043</t>
+          <t>615797</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>645201</t>
+          <t>645058</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1238803</t>
+          <t>1236118</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1276211</t>
+          <t>1277745</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14869</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35745</t>
+          <t>34524</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55951</t>
+          <t>53557</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87286</t>
+          <t>87362</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74861</t>
+          <t>76149</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>114061</t>
+          <t>116575</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>743353</t>
+          <t>744574</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>764229</t>
+          <t>765009</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>735292</t>
+          <t>735216</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>766627</t>
+          <t>769021</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1487615</t>
+          <t>1485101</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1526815</t>
+          <t>1525527</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>119409</t>
+          <t>118968</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>169596</t>
+          <t>168850</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>364180</t>
+          <t>366728</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>441185</t>
+          <t>444837</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>504880</t>
+          <t>506773</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>599533</t>
+          <t>597587</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3257183</t>
+          <t>3257929</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3307370</t>
+          <t>3307811</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3113913</t>
+          <t>3110261</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3190918</t>
+          <t>3188370</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6382344</t>
+          <t>6384290</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6476997</t>
+          <t>6475104</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2016</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24679</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30809</t>
+          <t>30576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55259</t>
+          <t>56241</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42344</t>
+          <t>42379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72665</t>
+          <t>72951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269082</t>
+          <t>268889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285722</t>
+          <t>285683</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>233444</t>
+          <t>232462</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257894</t>
+          <t>258127</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>509799</t>
+          <t>509513</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>540120</t>
+          <t>540085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>8516</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25019</t>
+          <t>24233</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37601</t>
+          <t>37253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65875</t>
+          <t>65514</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>51969</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85750</t>
+          <t>83621</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477556</t>
+          <t>478342</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>493792</t>
+          <t>494059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>457209</t>
+          <t>457570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485483</t>
+          <t>485831</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>939909</t>
+          <t>942038</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>973342</t>
+          <t>973690</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18742</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39069</t>
+          <t>38299</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21014</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43617</t>
+          <t>43010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308802</t>
+          <t>308751</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317569</t>
+          <t>317566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>297240</t>
+          <t>298010</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>317567</t>
+          <t>318210</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611257</t>
+          <t>611864</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>633860</t>
+          <t>633108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17891</t>
+          <t>16931</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38800</t>
+          <t>36223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25870</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50915</t>
+          <t>50209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351434</t>
+          <t>350580</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365019</t>
+          <t>364791</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348483</t>
+          <t>351060</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369392</t>
+          <t>370352</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>706332</t>
+          <t>707038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>731377</t>
+          <t>730072</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>19541</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18872</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>39116</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29691</t>
+          <t>28801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52418</t>
+          <t>51663</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191068</t>
+          <t>191680</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205287</t>
+          <t>204890</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179980</t>
+          <t>179471</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199715</t>
+          <t>199933</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377390</t>
+          <t>378145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400117</t>
+          <t>401007</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24595</t>
+          <t>25164</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46542</t>
+          <t>46731</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30487</t>
+          <t>30557</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53700</t>
+          <t>55783</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249354</t>
+          <t>250195</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260240</t>
+          <t>260300</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>226573</t>
+          <t>226384</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248520</t>
+          <t>247951</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>482538</t>
+          <t>480455</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>505751</t>
+          <t>505681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26181</t>
+          <t>25026</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44547</t>
+          <t>46191</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74685</t>
+          <t>76981</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56919</t>
+          <t>57987</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91352</t>
+          <t>93739</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>630377</t>
+          <t>631532</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648099</t>
+          <t>648206</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>616609</t>
+          <t>614313</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>646747</t>
+          <t>645103</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1256500</t>
+          <t>1254113</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1290933</t>
+          <t>1289865</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>22994</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46658</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76710</t>
+          <t>76309</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114751</t>
+          <t>115450</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>106291</t>
+          <t>106512</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>151517</t>
+          <t>154082</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>731925</t>
+          <t>733601</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>754988</t>
+          <t>755589</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>711416</t>
+          <t>710717</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>749457</t>
+          <t>749858</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1453233</t>
+          <t>1450668</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1498459</t>
+          <t>1498238</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>92138</t>
+          <t>91379</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>133487</t>
+          <t>132771</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>327383</t>
+          <t>323651</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>399455</t>
+          <t>398752</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>425952</t>
+          <t>434571</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>515234</t>
+          <t>519549</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3260863</t>
+          <t>3261579</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3302212</t>
+          <t>3302971</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3145087</t>
+          <t>3145790</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3217159</t>
+          <t>3220891</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6423658</t>
+          <t>6419343</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6512940</t>
+          <t>6504321</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2023</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12213</t>
+          <t>10976</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>20384</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14109</t>
+          <t>14545</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28115</t>
+          <t>27750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>299230</t>
+          <t>300467</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309474</t>
+          <t>309601</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269340</t>
+          <t>269251</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279740</t>
+          <t>279453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>572962</t>
+          <t>573327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>586968</t>
+          <t>586532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18834</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40907</t>
+          <t>42272</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57226</t>
+          <t>58139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83023</t>
+          <t>84663</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81247</t>
+          <t>81392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118767</t>
+          <t>117721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477483</t>
+          <t>476118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499556</t>
+          <t>499590</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>431946</t>
+          <t>430306</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>457743</t>
+          <t>456830</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>914592</t>
+          <t>915638</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952112</t>
+          <t>951967</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18907</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42544</t>
+          <t>43398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64237</t>
+          <t>64856</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67715</t>
+          <t>66811</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96861</t>
+          <t>95463</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277482</t>
+          <t>277446</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>297143</t>
+          <t>296606</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>284891</t>
+          <t>284272</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>306584</t>
+          <t>305730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>568317</t>
+          <t>569715</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>597463</t>
+          <t>598367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15983</t>
+          <t>15947</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>37004</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22244</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>52504</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44121</t>
+          <t>45230</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81683</t>
+          <t>80586</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274354</t>
+          <t>275553</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296574</t>
+          <t>296610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>423218</t>
+          <t>423214</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>453474</t>
+          <t>453546</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>706591</t>
+          <t>707688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>744153</t>
+          <t>743044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23701</t>
+          <t>23254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26956</t>
+          <t>26614</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171414</t>
+          <t>171585</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177544</t>
+          <t>177554</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>235078</t>
+          <t>235525</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>250192</t>
+          <t>251070</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410565</t>
+          <t>410907</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425615</t>
+          <t>424851</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>19942</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37018</t>
+          <t>36304</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48790</t>
+          <t>47285</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55195</t>
+          <t>54936</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80381</t>
+          <t>79247</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232618</t>
+          <t>233332</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249924</t>
+          <t>249694</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>208266</t>
+          <t>209771</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>225802</t>
+          <t>226459</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>446311</t>
+          <t>447445</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>471497</t>
+          <t>471756</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33106</t>
+          <t>32806</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61519</t>
+          <t>60436</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49286</t>
+          <t>48289</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>135942</t>
+          <t>137379</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90330</t>
+          <t>92420</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>176943</t>
+          <t>177779</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>562760</t>
+          <t>563843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>591173</t>
+          <t>591473</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>713323</t>
+          <t>711886</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>799979</t>
+          <t>800976</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1296601</t>
+          <t>1295765</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1383214</t>
+          <t>1381124</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51523</t>
+          <t>54877</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70008</t>
+          <t>70302</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97665</t>
+          <t>98047</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>76151</t>
+          <t>72753</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>147523</t>
+          <t>148206</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>877197</t>
+          <t>873843</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>914886</t>
+          <t>913843</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>620066</t>
+          <t>619684</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>647723</t>
+          <t>647429</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1498929</t>
+          <t>1498246</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1570301</t>
+          <t>1573699</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>156248</t>
+          <t>155788</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>231927</t>
+          <t>229127</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>333079</t>
+          <t>334413</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>458157</t>
+          <t>455450</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>533889</t>
+          <t>525435</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>673135</t>
+          <t>669137</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3227890</t>
+          <t>3230690</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3303569</t>
+          <t>3304029</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3254123</t>
+          <t>3256830</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3379201</t>
+          <t>3377867</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6498962</t>
+          <t>6502960</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6638208</t>
+          <t>6646662</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1423-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1423-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>17863</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38474</t>
+          <t>37409</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24550</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47234</t>
+          <t>49038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260028</t>
+          <t>259499</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270105</t>
+          <t>269478</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>222364</t>
+          <t>223429</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243849</t>
+          <t>242975</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>486614</t>
+          <t>484810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>509298</t>
+          <t>508966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>20306</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32984</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59584</t>
+          <t>59789</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45587</t>
+          <t>43900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74064</t>
+          <t>72729</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472479</t>
+          <t>472769</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487033</t>
+          <t>486791</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>444365</t>
+          <t>444160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470965</t>
+          <t>469748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>922960</t>
+          <t>924295</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>951437</t>
+          <t>953124</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14309</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32751</t>
+          <t>32638</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17213</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37947</t>
+          <t>37325</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307306</t>
+          <t>307730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317900</t>
+          <t>317918</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>302661</t>
+          <t>302774</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321103</t>
+          <t>320601</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616311</t>
+          <t>616933</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>637045</t>
+          <t>637187</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>16022</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26445</t>
+          <t>25583</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35181</t>
+          <t>34671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343051</t>
+          <t>342649</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355335</t>
+          <t>355344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345011</t>
+          <t>345873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361151</t>
+          <t>361193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>694946</t>
+          <t>695456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>714407</t>
+          <t>714583</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12489</t>
+          <t>12721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14407</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32237</t>
+          <t>31167</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19139</t>
+          <t>19642</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40265</t>
+          <t>41095</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>190819</t>
+          <t>190587</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199899</t>
+          <t>199953</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175431</t>
+          <t>176501</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193261</t>
+          <t>193588</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>370711</t>
+          <t>369881</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>391837</t>
+          <t>391334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6065</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23792</t>
+          <t>24539</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27375</t>
+          <t>26905</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264578</t>
+          <t>264746</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254352</t>
+          <t>253605</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269016</t>
+          <t>269013</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>521580</t>
+          <t>522050</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>538567</t>
+          <t>537965</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27065</t>
+          <t>27305</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>37912</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66033</t>
+          <t>66929</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54500</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86196</t>
+          <t>88063</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>587962</t>
+          <t>587722</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>603618</t>
+          <t>603818</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>572186</t>
+          <t>571290</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>599886</t>
+          <t>600307</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1167050</t>
+          <t>1165183</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1198746</t>
+          <t>1197824</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32070</t>
+          <t>33022</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>59087</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44506</t>
+          <t>44841</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73742</t>
+          <t>77174</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82536</t>
+          <t>82417</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>124677</t>
+          <t>120581</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>684748</t>
+          <t>684708</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>711725</t>
+          <t>710773</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>709769</t>
+          <t>706337</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>739005</t>
+          <t>738670</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1402629</t>
+          <t>1406725</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1444770</t>
+          <t>1444889</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>82672</t>
+          <t>83266</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>122507</t>
+          <t>121468</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>226997</t>
+          <t>222029</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>288276</t>
+          <t>284522</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>326547</t>
+          <t>318267</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>396959</t>
+          <t>393864</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3154036</t>
+          <t>3155075</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3193871</t>
+          <t>3193277</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3090921</t>
+          <t>3094675</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3152200</t>
+          <t>3157168</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6258782</t>
+          <t>6261877</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6329194</t>
+          <t>6337474</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25101</t>
+          <t>24831</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47980</t>
+          <t>47621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37889</t>
+          <t>37975</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65386</t>
+          <t>65934</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>271544</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286248</t>
+          <t>286134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239265</t>
+          <t>239624</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262144</t>
+          <t>262414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516597</t>
+          <t>516049</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>544094</t>
+          <t>544008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33408</t>
+          <t>31015</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50001</t>
+          <t>51151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82553</t>
+          <t>82987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66445</t>
+          <t>66044</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104817</t>
+          <t>105140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472119</t>
+          <t>474512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494674</t>
+          <t>495602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441212</t>
+          <t>440778</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>473764</t>
+          <t>472614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>924475</t>
+          <t>924152</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>962847</t>
+          <t>963248</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27907</t>
+          <t>27498</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27581</t>
+          <t>27631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52107</t>
+          <t>51976</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41665</t>
+          <t>42781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69788</t>
+          <t>71809</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296139</t>
+          <t>296548</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314011</t>
+          <t>313237</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>288913</t>
+          <t>289044</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>313439</t>
+          <t>313389</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>595278</t>
+          <t>593257</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>623401</t>
+          <t>622285</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17228</t>
+          <t>18114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68534</t>
+          <t>66641</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46929</t>
+          <t>48369</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79202</t>
+          <t>78803</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356754</t>
+          <t>355868</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369842</t>
+          <t>369751</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320417</t>
+          <t>322310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>347391</t>
+          <t>349237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>683731</t>
+          <t>684130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>716004</t>
+          <t>714564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33536</t>
+          <t>34116</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57497</t>
+          <t>58353</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41275</t>
+          <t>41820</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70252</t>
+          <t>68642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193628</t>
+          <t>194017</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207502</t>
+          <t>207109</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>162094</t>
+          <t>161238</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186055</t>
+          <t>185475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>361957</t>
+          <t>363567</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>390934</t>
+          <t>390389</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,32%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24099</t>
+          <t>23297</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27395</t>
+          <t>25526</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49691</t>
+          <t>49140</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37615</t>
+          <t>39276</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66153</t>
+          <t>67073</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249882</t>
+          <t>250684</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266022</t>
+          <t>266200</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>228405</t>
+          <t>228956</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250701</t>
+          <t>252570</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>485924</t>
+          <t>485004</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>514462</t>
+          <t>512801</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23622</t>
+          <t>24055</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49699</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48795</t>
+          <t>49621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78056</t>
+          <t>79965</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78896</t>
+          <t>80633</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>120523</t>
+          <t>116834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>613089</t>
+          <t>613957</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>639166</t>
+          <t>638733</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>615797</t>
+          <t>613888</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>645058</t>
+          <t>644232</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1236118</t>
+          <t>1239807</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1277745</t>
+          <t>1276008</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14089</t>
+          <t>15165</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34524</t>
+          <t>34980</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53557</t>
+          <t>54272</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87362</t>
+          <t>86499</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>76149</t>
+          <t>75149</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>116575</t>
+          <t>115454</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>744574</t>
+          <t>744118</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>765009</t>
+          <t>763933</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>735216</t>
+          <t>736079</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>769021</t>
+          <t>768306</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1485101</t>
+          <t>1486222</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1525527</t>
+          <t>1526527</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>118968</t>
+          <t>117403</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>168850</t>
+          <t>170544</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>366728</t>
+          <t>371315</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>444837</t>
+          <t>444017</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>506773</t>
+          <t>504603</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>597587</t>
+          <t>594476</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3257929</t>
+          <t>3256235</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3307811</t>
+          <t>3309376</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3110261</t>
+          <t>3111081</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3188370</t>
+          <t>3183783</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6384290</t>
+          <t>6387401</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6475104</t>
+          <t>6477274</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24872</t>
+          <t>24256</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30576</t>
+          <t>30791</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56241</t>
+          <t>55414</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42379</t>
+          <t>43023</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72951</t>
+          <t>74463</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>268889</t>
+          <t>269505</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285683</t>
+          <t>285675</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232462</t>
+          <t>233289</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258127</t>
+          <t>257912</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>509513</t>
+          <t>508001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>540085</t>
+          <t>539441</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24233</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37253</t>
+          <t>38279</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65514</t>
+          <t>67441</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51969</t>
+          <t>52341</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83621</t>
+          <t>85463</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>478342</t>
+          <t>478483</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494059</t>
+          <t>493967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>457570</t>
+          <t>455643</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485831</t>
+          <t>484805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>942038</t>
+          <t>940196</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>973690</t>
+          <t>973318</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9814</t>
+          <t>10498</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>17568</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38299</t>
+          <t>37721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43010</t>
+          <t>43443</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308751</t>
+          <t>308067</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317566</t>
+          <t>317557</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>298010</t>
+          <t>298588</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>318210</t>
+          <t>318741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611864</t>
+          <t>611431</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>633108</t>
+          <t>634276</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19384</t>
+          <t>19646</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16931</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36223</t>
+          <t>37758</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27175</t>
+          <t>26371</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50209</t>
+          <t>49737</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>350580</t>
+          <t>350318</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>364791</t>
+          <t>364211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>351060</t>
+          <t>349525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>370352</t>
+          <t>370518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707038</t>
+          <t>707510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>730072</t>
+          <t>730876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>18605</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18654</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39116</t>
+          <t>38324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28466</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51663</t>
+          <t>51579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191680</t>
+          <t>192616</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204890</t>
+          <t>205440</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>179471</t>
+          <t>180263</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199933</t>
+          <t>199463</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>378145</t>
+          <t>378229</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>401007</t>
+          <t>401342</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>13390</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25164</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46731</t>
+          <t>46837</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30557</t>
+          <t>29342</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55783</t>
+          <t>55397</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250195</t>
+          <t>249733</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260300</t>
+          <t>260179</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>226384</t>
+          <t>226278</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247951</t>
+          <t>249397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>480455</t>
+          <t>480841</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>505681</t>
+          <t>506896</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>23991</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46191</t>
+          <t>44890</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76981</t>
+          <t>75862</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57987</t>
+          <t>58427</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93739</t>
+          <t>95602</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>631532</t>
+          <t>632567</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648206</t>
+          <t>647913</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>614313</t>
+          <t>615432</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>645103</t>
+          <t>646404</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1254113</t>
+          <t>1252250</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1289865</t>
+          <t>1289425</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22994</t>
+          <t>21997</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44982</t>
+          <t>43481</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76309</t>
+          <t>76173</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115450</t>
+          <t>116120</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>106512</t>
+          <t>104679</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>154082</t>
+          <t>153208</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>733601</t>
+          <t>735102</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>755589</t>
+          <t>756586</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>710717</t>
+          <t>710047</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>749858</t>
+          <t>749994</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1450668</t>
+          <t>1451542</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1498238</t>
+          <t>1500071</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>91379</t>
+          <t>91904</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>132771</t>
+          <t>132452</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>323651</t>
+          <t>323335</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>398752</t>
+          <t>399186</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>434571</t>
+          <t>434479</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>519549</t>
+          <t>521099</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3261579</t>
+          <t>3261898</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3302971</t>
+          <t>3302446</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3145790</t>
+          <t>3145356</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3220891</t>
+          <t>3221207</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6419343</t>
+          <t>6417793</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6504321</t>
+          <t>6504413</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10976</t>
+          <t>10341</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20384</t>
+          <t>22520</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>15082</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27750</t>
+          <t>28783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>305966</t>
+          <t>313770</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>300467</t>
+          <t>308504</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309601</t>
+          <t>317163</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>274978</t>
+          <t>300125</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269251</t>
+          <t>293541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279453</t>
+          <t>304968</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>580943</t>
+          <t>613895</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573327</t>
+          <t>606123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>586532</t>
+          <t>619824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28758</t>
+          <t>30495</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18800</t>
+          <t>20540</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42272</t>
+          <t>44131</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69824</t>
+          <t>75192</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58139</t>
+          <t>61937</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84663</t>
+          <t>88719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>98582</t>
+          <t>105687</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81392</t>
+          <t>88692</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117721</t>
+          <t>125601</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>489632</t>
+          <t>500152</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>476118</t>
+          <t>486516</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499590</t>
+          <t>510107</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>445145</t>
+          <t>471302</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>430306</t>
+          <t>457775</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>456830</t>
+          <t>484557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>934777</t>
+          <t>971454</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>915638</t>
+          <t>951540</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>951967</t>
+          <t>988449</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27403</t>
+          <t>29020</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t>20234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>39326</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52976</t>
+          <t>54094</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43398</t>
+          <t>44234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64856</t>
+          <t>65366</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>80378</t>
+          <t>83115</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66811</t>
+          <t>69337</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95463</t>
+          <t>97456</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>288647</t>
+          <t>286973</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277446</t>
+          <t>276667</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>296606</t>
+          <t>295759</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>296152</t>
+          <t>302287</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>284272</t>
+          <t>291015</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>305730</t>
+          <t>312147</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>584800</t>
+          <t>589260</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>569715</t>
+          <t>574919</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>598367</t>
+          <t>603038</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>26633</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15947</t>
+          <t>17495</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37004</t>
+          <t>40098</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38582</t>
+          <t>41431</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52504</t>
+          <t>54491</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>63420</t>
+          <t>68063</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>54236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80586</t>
+          <t>83927</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>287719</t>
+          <t>346512</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275553</t>
+          <t>333047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296610</t>
+          <t>355650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>437136</t>
+          <t>380530</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>423214</t>
+          <t>367470</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>453546</t>
+          <t>389420</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>724854</t>
+          <t>727044</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707688</t>
+          <t>711180</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>743044</t>
+          <t>740871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>12286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23254</t>
+          <t>23903</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>20156</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26614</t>
+          <t>28362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>175756</t>
+          <t>202528</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171585</t>
+          <t>198371</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177554</t>
+          <t>204481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>242678</t>
+          <t>211899</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>235525</t>
+          <t>205015</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>251070</t>
+          <t>216632</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>418434</t>
+          <t>414426</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410907</t>
+          <t>406220</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424851</t>
+          <t>419808</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27441</t>
+          <t>27413</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36304</t>
+          <t>36178</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38794</t>
+          <t>39311</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>31267</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47285</t>
+          <t>48651</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>66235</t>
+          <t>66724</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54936</t>
+          <t>55961</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79247</t>
+          <t>78629</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>242195</t>
+          <t>243294</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233332</t>
+          <t>234529</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249694</t>
+          <t>250853</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>218262</t>
+          <t>224439</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>209771</t>
+          <t>215099</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226459</t>
+          <t>232483</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>460457</t>
+          <t>467733</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>447445</t>
+          <t>455828</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>471756</t>
+          <t>478496</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,102 +12755,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>45270</t>
+          <t>52462</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32806</t>
+          <t>38654</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60436</t>
+          <t>69367</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>9,64%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>116236</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>98795</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>136658</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>17,7%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>168698</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>144418</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>192182</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>9,68%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>98369</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>48289</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>137379</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>11,58%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>143639</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>92420</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>177779</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -12868,102 +12868,102 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>579009</t>
+          <t>667225</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>563843</t>
+          <t>650320</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>591473</t>
+          <t>681033</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>94,63%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>655821</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>635399</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>673262</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>84,94%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>82,3%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>87,2%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1366</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1323046</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1299562</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1347326</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>88,69%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>87,12%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>90,32%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>750896</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>711886</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>800976</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>88,42%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>83,82%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>94,31%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1366</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1329905</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1295765</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1381124</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>90,25%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>87,94%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>35195</t>
+          <t>40812</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14877</t>
+          <t>29731</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54877</t>
+          <t>56450</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>83824</t>
+          <t>97412</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>70302</t>
+          <t>82450</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98047</t>
+          <t>115514</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>119019</t>
+          <t>138224</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72753</t>
+          <t>119798</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>148206</t>
+          <t>158383</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>893525</t>
+          <t>757260</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>873843</t>
+          <t>741622</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>913843</t>
+          <t>768341</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>633907</t>
+          <t>733919</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>619684</t>
+          <t>715817</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>647429</t>
+          <t>748881</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1527433</t>
+          <t>1491179</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1498246</t>
+          <t>1471020</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1573699</t>
+          <t>1509605</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>197367</t>
+          <t>215047</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>155788</t>
+          <t>186900</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>229127</t>
+          <t>247797</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>413127</t>
+          <t>456631</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>334413</t>
+          <t>422986</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>455450</t>
+          <t>493459</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>610494</t>
+          <t>671678</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>525435</t>
+          <t>620917</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>669137</t>
+          <t>712908</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3262450</t>
+          <t>3317715</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3230690</t>
+          <t>3284965</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3304029</t>
+          <t>3345862</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3299153</t>
+          <t>3280323</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3256830</t>
+          <t>3243495</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3377867</t>
+          <t>3313968</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6561603</t>
+          <t>6598038</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6502960</t>
+          <t>6556808</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6646662</t>
+          <t>6648799</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
